--- a/vehicle_inspection_forms/004_straight_truck_pre_trip_inspection_form--vehicle_inspection_forms.xlsx
+++ b/vehicle_inspection_forms/004_straight_truck_pre_trip_inspection_form--vehicle_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'dry_van'}</t>
+          <t>dry_van</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Dry Van'}</t>
+          <t>Dry Van</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'reefer_van'}</t>
+          <t>reefer_van</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Reefer Van'}</t>
+          <t>Reefer Van</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'conventional'}</t>
+          <t>conventional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Conventional'}</t>
+          <t>Conventional</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'tanker'}</t>
+          <t>tanker</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Tanker'}</t>
+          <t>Tanker</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'normal_operation'}</t>
+          <t>normal_operation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Normal Operation'}</t>
+          <t>Normal Operation</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'warning'}</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Warning'}</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'malfunction'}</t>
+          <t>malfunction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Malfunction'}</t>
+          <t>Malfunction</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'normal_operation'}</t>
+          <t>normal_operation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Normal Operation'}</t>
+          <t>Normal Operation</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'stiff'}</t>
+          <t>stiff</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Stiff'}</t>
+          <t>Stiff</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'malfunction'}</t>
+          <t>malfunction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Malfunction'}</t>
+          <t>Malfunction</t>
         </is>
       </c>
     </row>
